--- a/Results/Glucagon Proportions/Glucagon_Content_AO_Analysis.xlsx
+++ b/Results/Glucagon Proportions/Glucagon_Content_AO_Analysis.xlsx
@@ -1519,13 +1519,13 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2575</v>
+        <v>0.2381</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1726</v>
+        <v>0.165</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3469</v>
+        <v>0.3151</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1539,19 +1539,19 @@
         <v>112</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2962</v>
+        <v>0.2145</v>
       </c>
       <c r="C7" t="n">
-        <v>0.129</v>
+        <v>0.0692</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4503</v>
+        <v>0.3572</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9998</v>
+        <v>0.996</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="8">
@@ -1559,13 +1559,13 @@
         <v>113</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.2863</v>
+        <v>-0.22</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3632</v>
+        <v>-0.2904</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2068</v>
+        <v>-0.1449</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1579,19 +1579,19 @@
         <v>114</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0286</v>
+        <v>0.0177</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1156</v>
+        <v>-0.0506</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0535</v>
+        <v>0.089</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2648</v>
+        <v>0.6945</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7352</v>
+        <v>0.3055</v>
       </c>
     </row>
     <row r="10">
@@ -1599,19 +1599,19 @@
         <v>115</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.2566</v>
+        <v>-0.245</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.4123</v>
+        <v>-0.3913</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0823</v>
+        <v>-0.0975</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0025</v>
+        <v>0.0005</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9975</v>
+        <v>0.9995</v>
       </c>
     </row>
     <row r="11">
@@ -1619,19 +1619,19 @@
         <v>116</v>
       </c>
       <c r="B11" t="n">
-        <v>0.008</v>
+        <v>-0.0048</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1707</v>
+        <v>-0.1433</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1898</v>
+        <v>0.1381</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5337</v>
+        <v>0.473</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4662</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="12">
@@ -1639,19 +1639,19 @@
         <v>117</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0306</v>
+        <v>0.0236</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1733</v>
+        <v>-0.13</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1125</v>
+        <v>0.1729</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3198</v>
+        <v>0.6272</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6802</v>
+        <v>0.3728</v>
       </c>
     </row>
     <row r="13">
@@ -1659,19 +1659,19 @@
         <v>118</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2277</v>
+        <v>0.2627</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0665</v>
+        <v>0.1239</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4034</v>
+        <v>0.4196</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9938</v>
+        <v>0.9998</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0063</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="14">
@@ -1679,13 +1679,13 @@
         <v>119</v>
       </c>
       <c r="B14" t="n">
-        <v>0.265</v>
+        <v>0.2384</v>
       </c>
       <c r="C14" t="n">
-        <v>0.185</v>
+        <v>0.1631</v>
       </c>
       <c r="D14" t="n">
-        <v>0.343</v>
+        <v>0.3109</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1699,19 +1699,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.036</v>
+        <v>0.0234</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2234</v>
+        <v>-0.1119</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1388</v>
+        <v>0.1678</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3375</v>
+        <v>0.6388</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6625</v>
+        <v>0.3612</v>
       </c>
     </row>
     <row r="16">
@@ -1719,19 +1719,19 @@
         <v>121</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.398</v>
+        <v>-0.2645</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5445</v>
+        <v>-0.3929</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2378</v>
+        <v>-0.1139</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="17">
@@ -1739,19 +1739,19 @@
         <v>122</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.1382</v>
+        <v>-0.0253</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3174</v>
+        <v>-0.1613</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0426</v>
+        <v>0.112</v>
       </c>
       <c r="E17" t="n">
-        <v>0.061</v>
+        <v>0.3498</v>
       </c>
       <c r="F17" t="n">
-        <v>0.939</v>
+        <v>0.6502</v>
       </c>
     </row>
     <row r="18">
@@ -1759,19 +1759,19 @@
         <v>123</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.1103</v>
+        <v>-0.0448</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2772</v>
+        <v>-0.1726</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0614</v>
+        <v>0.0955</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1047</v>
+        <v>0.262</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8952</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="19">
@@ -1779,13 +1779,13 @@
         <v>124</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.3661</v>
+        <v>-0.287</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.4343</v>
+        <v>-0.3555</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.299</v>
+        <v>-0.2181</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1799,19 +1799,19 @@
         <v>125</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.1011</v>
+        <v>-0.0481</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1719</v>
+        <v>-0.1173</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0252</v>
+        <v>0.0136</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0053</v>
+        <v>0.066</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9948</v>
+        <v>0.934</v>
       </c>
     </row>
   </sheetData>
@@ -1854,13 +1854,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2365</v>
+        <v>0.4134</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1702</v>
+        <v>0.3324</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3158</v>
+        <v>0.4974</v>
       </c>
     </row>
     <row r="5">
@@ -1868,13 +1868,13 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4993</v>
+        <v>0.6539</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4052</v>
+        <v>0.5703</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5991</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="6">
@@ -1882,13 +1882,13 @@
         <v>51</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5646</v>
+        <v>0.6689</v>
       </c>
       <c r="C6" t="n">
-        <v>0.478</v>
+        <v>0.5989</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6551</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="7">
@@ -1926,13 +1926,13 @@
         <v>58</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.2609</v>
+        <v>-0.2382</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3215</v>
+        <v>-0.2953</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1913</v>
+        <v>-0.1854</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1946,13 +1946,13 @@
         <v>59</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.3267</v>
+        <v>-0.2538</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3796</v>
+        <v>-0.3032</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2677</v>
+        <v>-0.2023</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1966,19 +1966,19 @@
         <v>60</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0654</v>
+        <v>-0.0157</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1254</v>
+        <v>-0.0627</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0003</v>
+        <v>0.0355</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0213</v>
+        <v>0.2842</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9788</v>
+        <v>0.7158</v>
       </c>
     </row>
   </sheetData>
@@ -2021,13 +2021,13 @@
         <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.404</v>
+        <v>0.5798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3029</v>
+        <v>0.4905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5193</v>
+        <v>0.6647</v>
       </c>
     </row>
     <row r="5">
@@ -2035,13 +2035,13 @@
         <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4638</v>
+        <v>0.5773</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3594</v>
+        <v>0.4726</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5795</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="6">
@@ -2079,19 +2079,19 @@
         <v>66</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0582</v>
+        <v>0.0018</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2197</v>
+        <v>-0.1301</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0893</v>
+        <v>0.133</v>
       </c>
       <c r="E9" t="n">
-        <v>0.214</v>
+        <v>0.5102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.786</v>
+        <v>0.4898</v>
       </c>
     </row>
   </sheetData>
@@ -2140,13 +2140,13 @@
         <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2197</v>
+        <v>0.4258</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1319</v>
+        <v>0.3272</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3208</v>
+        <v>0.5325</v>
       </c>
     </row>
     <row r="5">
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2502</v>
+        <v>0.401</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1512</v>
+        <v>0.2776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3551</v>
+        <v>0.5159</v>
       </c>
     </row>
     <row r="6">
@@ -2174,13 +2174,13 @@
         <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4796</v>
+        <v>0.6653</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3413</v>
+        <v>0.5603</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6039</v>
+        <v>0.7533</v>
       </c>
     </row>
     <row r="7">
@@ -2191,13 +2191,13 @@
         <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>0.519</v>
+        <v>0.6425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3923</v>
+        <v>0.5354</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6528</v>
+        <v>0.7546</v>
       </c>
     </row>
     <row r="8">
@@ -2208,13 +2208,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5094</v>
+        <v>0.6477</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3837</v>
+        <v>0.5543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6302</v>
+        <v>0.7379</v>
       </c>
     </row>
     <row r="9">
@@ -2225,13 +2225,13 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6219</v>
+        <v>0.6911</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4977</v>
+        <v>0.5891</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7388</v>
+        <v>0.7939</v>
       </c>
     </row>
     <row r="10">
@@ -2275,19 +2275,19 @@
         <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0306</v>
+        <v>0.0236</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1733</v>
+        <v>-0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1125</v>
+        <v>0.1729</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3198</v>
+        <v>0.6272</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6802</v>
+        <v>0.3728</v>
       </c>
     </row>
     <row r="14">
@@ -2298,19 +2298,19 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.036</v>
+        <v>0.0234</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2234</v>
+        <v>-0.1119</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1388</v>
+        <v>0.1678</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3375</v>
+        <v>0.6388</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6625</v>
+        <v>0.3612</v>
       </c>
     </row>
     <row r="15">
@@ -2321,19 +2321,19 @@
         <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1103</v>
+        <v>-0.0448</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2772</v>
+        <v>-0.1726</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0614</v>
+        <v>0.0955</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1047</v>
+        <v>0.262</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8952</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="16">
@@ -2377,13 +2377,13 @@
         <v>63</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2575</v>
+        <v>-0.2381</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3469</v>
+        <v>-0.3151</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1726</v>
+        <v>-0.165</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2400,13 +2400,13 @@
         <v>63</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2863</v>
+        <v>-0.22</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3632</v>
+        <v>-0.2904</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2068</v>
+        <v>-0.1449</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2423,19 +2423,19 @@
         <v>63</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0286</v>
+        <v>0.0177</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1156</v>
+        <v>-0.0506</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0535</v>
+        <v>0.089</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2648</v>
+        <v>0.6945</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7352</v>
+        <v>0.3055</v>
       </c>
     </row>
     <row r="22">
@@ -2446,13 +2446,13 @@
         <v>64</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.265</v>
+        <v>-0.2384</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.343</v>
+        <v>-0.3109</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.185</v>
+        <v>-0.1631</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2469,13 +2469,13 @@
         <v>64</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.3661</v>
+        <v>-0.287</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4343</v>
+        <v>-0.3555</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.299</v>
+        <v>-0.2181</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2492,19 +2492,19 @@
         <v>64</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1011</v>
+        <v>-0.0481</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1719</v>
+        <v>-0.1173</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0252</v>
+        <v>0.0136</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0053</v>
+        <v>0.066</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9948</v>
+        <v>0.934</v>
       </c>
     </row>
   </sheetData>
@@ -2558,13 +2558,13 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0289</v>
+        <v>0.0261</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0145</v>
+        <v>0.0134</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0439</v>
+        <v>0.0398</v>
       </c>
       <c r="E5" t="n">
         <v>0.9998</v>
@@ -2608,19 +2608,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0199</v>
+        <v>0.0241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0065</v>
+        <v>0.0082</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0323</v>
+        <v>0.0382</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9962</v>
+        <v>0.9988</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0037</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="10">
@@ -2628,19 +2628,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0408</v>
+        <v>0.0299</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0224</v>
+        <v>0.0153</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0588</v>
+        <v>0.0449</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.9995</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="11">
@@ -2648,19 +2648,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0258</v>
+        <v>0.0241</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0082</v>
+        <v>0.0103</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0442</v>
+        <v>0.0385</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9975</v>
+        <v>0.9995</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0025</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="12">
@@ -2698,19 +2698,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0212</v>
+        <v>-0.0061</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0337</v>
+        <v>-0.0173</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.007</v>
+        <v>0.0052</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0015</v>
+        <v>0.1545</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9985</v>
+        <v>0.8455</v>
       </c>
     </row>
     <row r="16">
@@ -2718,19 +2718,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0062</v>
+        <v>-0.0002</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.019</v>
+        <v>-0.0121</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0076</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1828</v>
+        <v>0.4905</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8172</v>
+        <v>0.5095</v>
       </c>
     </row>
     <row r="17">
@@ -2738,19 +2738,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>0.015</v>
+        <v>0.0057</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0008</v>
+        <v>-0.0041</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0285</v>
+        <v>0.0161</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9808</v>
+        <v>0.8685</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0192</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="18">
@@ -2788,19 +2788,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>0.026</v>
+        <v>0.0232</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0068</v>
+        <v>0.0052</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0429</v>
+        <v>0.0398</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9938</v>
+        <v>0.9935</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0063</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="22">
@@ -2808,19 +2808,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0321</v>
+        <v>0.0291</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0133</v>
+        <v>0.009</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0524</v>
+        <v>0.0479</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9975</v>
+        <v>0.997</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="23">
@@ -2858,19 +2858,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0062</v>
+        <v>-0.0057</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0297</v>
+        <v>-0.0319</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0171</v>
+        <v>0.0184</v>
       </c>
       <c r="E26" t="n">
-        <v>0.306</v>
+        <v>0.325</v>
       </c>
       <c r="F26" t="n">
-        <v>0.694</v>
+        <v>0.675</v>
       </c>
     </row>
   </sheetData>
@@ -2924,19 +2924,19 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0007</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.015</v>
+        <v>-0.0093</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0039</v>
+        <v>0.0082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1102</v>
+        <v>0.4363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8898</v>
+        <v>0.5638</v>
       </c>
     </row>
     <row r="6">
@@ -2974,19 +2974,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0176</v>
+        <v>-0.0148</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.0052</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0235</v>
+        <v>0.183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9765</v>
+        <v>0.817</v>
       </c>
     </row>
     <row r="10">
@@ -2994,19 +2994,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0052</v>
+        <v>0.0015</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0164</v>
+        <v>-0.0078</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0056</v>
+        <v>0.0114</v>
       </c>
       <c r="E10" t="n">
-        <v>0.175</v>
+        <v>0.6262</v>
       </c>
       <c r="F10" t="n">
-        <v>0.825</v>
+        <v>0.3738</v>
       </c>
     </row>
     <row r="11">
@@ -3014,19 +3014,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0038</v>
+        <v>0.0008</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0144</v>
+        <v>-0.0083</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2335</v>
+        <v>0.5738</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7665</v>
+        <v>0.4262</v>
       </c>
     </row>
     <row r="12">
@@ -3064,19 +3064,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0031</v>
+        <v>-0.0059</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0105</v>
+        <v>-0.0123</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004</v>
+        <v>0.0012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.186</v>
+        <v>0.0412</v>
       </c>
       <c r="F15" t="n">
-        <v>0.814</v>
+        <v>0.9588</v>
       </c>
     </row>
     <row r="16">
@@ -3084,19 +3084,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0046</v>
+        <v>-0.0054</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0118</v>
+        <v>-0.0119</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0018</v>
+        <v>0.0012</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0938</v>
+        <v>0.0532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9062</v>
+        <v>0.9468</v>
       </c>
     </row>
     <row r="17">
@@ -3104,19 +3104,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0014</v>
+        <v>0.0007</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.008</v>
+        <v>-0.0051</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0051</v>
+        <v>0.0069</v>
       </c>
       <c r="E17" t="n">
-        <v>0.334</v>
+        <v>0.5852</v>
       </c>
       <c r="F17" t="n">
-        <v>0.666</v>
+        <v>0.4148</v>
       </c>
     </row>
     <row r="18">
@@ -3154,19 +3154,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0127</v>
+        <v>-0.0078</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0226</v>
+        <v>-0.0178</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0043</v>
+        <v>0.0012</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006</v>
+        <v>0.0512</v>
       </c>
       <c r="F21" t="n">
-        <v>0.994</v>
+        <v>0.9488</v>
       </c>
     </row>
     <row r="22">
@@ -3174,19 +3174,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>0.001</v>
+        <v>0.0065</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0142</v>
+        <v>-0.0087</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0171</v>
+        <v>0.0213</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5582</v>
+        <v>0.8012</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4417</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="23">
@@ -3224,19 +3224,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0139</v>
+        <v>-0.0142</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0307</v>
+        <v>-0.0317</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0605</v>
+        <v>0.057</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9395</v>
+        <v>0.943</v>
       </c>
     </row>
   </sheetData>
@@ -3290,13 +3290,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0245</v>
+        <v>0.0294</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0203</v>
+        <v>0.0265</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0284</v>
+        <v>0.0325</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3340,13 +3340,13 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0382</v>
+        <v>0.0546</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0306</v>
+        <v>0.0494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0459</v>
+        <v>0.0602</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3360,13 +3360,13 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.025</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0182</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0321</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3380,19 +3380,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01</v>
+        <v>0.0149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0046</v>
+        <v>0.0106</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0156</v>
+        <v>0.0194</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3430,19 +3430,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0131</v>
+        <v>0.0358</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0029</v>
+        <v>0.0269</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0236</v>
+        <v>0.0436</v>
       </c>
       <c r="E15" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3450,13 +3450,13 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0282</v>
+        <v>0.0396</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0191</v>
+        <v>0.0329</v>
       </c>
       <c r="D16" t="n">
-        <v>0.038</v>
+        <v>0.0472</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -3470,19 +3470,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0149</v>
+        <v>0.0038</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0237</v>
+        <v>0.011</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9982</v>
+        <v>0.8512</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0018</v>
+        <v>0.1488</v>
       </c>
     </row>
     <row r="18">
@@ -3520,13 +3520,13 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>0.033</v>
+        <v>0.0385</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0269</v>
+        <v>0.0341</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0388</v>
+        <v>0.0432</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -3540,13 +3540,13 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="C22" t="n">
         <v>0.0161</v>
       </c>
-      <c r="C22" t="n">
-        <v>0.0111</v>
-      </c>
       <c r="D22" t="n">
-        <v>0.0208</v>
+        <v>0.0243</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -3590,13 +3590,13 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0169</v>
+        <v>0.0181</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0094</v>
+        <v>0.0115</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0241</v>
+        <v>0.0242</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -3677,19 +3677,19 @@
         <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0188</v>
+        <v>0.0223</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0052</v>
+        <v>0.0081</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03</v>
+        <v>0.0367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.996</v>
+        <v>0.9982</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="9">
@@ -3700,19 +3700,19 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0389</v>
+        <v>0.0281</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0211</v>
+        <v>0.0146</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0559</v>
+        <v>0.0436</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9998</v>
+        <v>0.9995</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="10">
@@ -3723,19 +3723,19 @@
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0246</v>
+        <v>0.023</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0078</v>
+        <v>0.0092</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0419</v>
+        <v>0.0369</v>
       </c>
       <c r="F10" t="n">
-        <v>0.997</v>
+        <v>0.9995</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="11">
@@ -3746,19 +3746,19 @@
         <v>97</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0211</v>
+        <v>0.026</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0069</v>
+        <v>0.0096</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0336</v>
+        <v>0.0407</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9962</v>
+        <v>0.999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0037</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
@@ -3769,19 +3769,19 @@
         <v>97</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0428</v>
+        <v>0.0317</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0242</v>
+        <v>0.0165</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0626</v>
+        <v>0.047</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="13">
@@ -3792,19 +3792,19 @@
         <v>97</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0271</v>
+        <v>0.0252</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0451</v>
+        <v>0.0399</v>
       </c>
       <c r="F13" t="n">
-        <v>0.997</v>
+        <v>0.9995</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="14">
@@ -3848,19 +3848,19 @@
         <v>99</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0023</v>
+        <v>0.0038</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0047</v>
+        <v>0.0076</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9738</v>
+        <v>0.9815</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0262</v>
+        <v>0.0185</v>
       </c>
     </row>
     <row r="18">
@@ -3871,19 +3871,19 @@
         <v>99</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0005</v>
+        <v>0.0002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0073</v>
+        <v>0.0061</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9868</v>
+        <v>0.987</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0132</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="19">
@@ -3894,19 +3894,19 @@
         <v>99</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0026</v>
+        <v>0.0022</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0011</v>
+        <v>-0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0056</v>
+        <v>0.0049</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>0.9248</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07</v>
+        <v>0.0752</v>
       </c>
     </row>
   </sheetData>
@@ -3981,19 +3981,19 @@
         <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0162</v>
+        <v>0.0208</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0036</v>
+        <v>0.0063</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0272</v>
+        <v>0.0354</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9928</v>
+        <v>0.9968</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0073</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="9">
@@ -4004,19 +4004,19 @@
         <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0417</v>
+        <v>0.0314</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0244</v>
+        <v>0.017</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0607</v>
+        <v>0.0472</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="10">
@@ -4027,19 +4027,19 @@
         <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0233</v>
+        <v>0.0221</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0061</v>
+        <v>0.0088</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0421</v>
+        <v>0.0375</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9945</v>
+        <v>0.9985</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0055</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="11">
@@ -4050,19 +4050,19 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0238</v>
+        <v>0.0271</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0083</v>
+        <v>0.0114</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0362</v>
+        <v>0.0418</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9988</v>
+        <v>0.9998</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0013</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="12">
@@ -4073,19 +4073,19 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0398</v>
+        <v>0.0283</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0213</v>
+        <v>0.0146</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0581</v>
+        <v>0.0437</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9995</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="13">
@@ -4096,19 +4096,19 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0284</v>
+        <v>0.0259</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0105</v>
+        <v>0.0127</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0464</v>
+        <v>0.0408</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9985</v>
+        <v>0.9998</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0015</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="14">
@@ -4152,13 +4152,13 @@
         <v>108</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0077</v>
+        <v>0.0063</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0049</v>
+        <v>0.0037</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0103</v>
+        <v>0.0089</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -4175,19 +4175,19 @@
         <v>108</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0018</v>
+        <v>-0.003</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0044</v>
+        <v>-0.0055</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0011</v>
+        <v>-0.0007</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1055</v>
+        <v>0.0082</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8945</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="19">
@@ -4198,13 +4198,13 @@
         <v>108</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0052</v>
+        <v>0.0038</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0031</v>
+        <v>0.0019</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0072</v>
+        <v>0.0061</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
